--- a/backend/storage/imports/Master_SBM/Honorarium 36 SATUAN BIAYA PENGADAAN KENDARAAN DINAS.xlsx
+++ b/backend/storage/imports/Master_SBM/Honorarium 36 SATUAN BIAYA PENGADAAN KENDARAAN DINAS.xlsx
@@ -5,10 +5,10 @@
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="X:\dokumen perkuliahan\kebutuhan magang\Projek magang\DITUGASKAN\SBM\baru\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\UNIVERSITAS BINA SARANA INFORMATIKA(UBSI)\FILE MAGANG\Aplikasi Realisasi Keuangan\Relai\backend\storage\imports\Master_SBM\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{229E8896-9349-4720-9238-2FB6AC844E7E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{96BA0EC9-ACEC-41F1-981D-D89340E87935}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{F7C555FD-74F2-4F3D-B792-2C41B5A49CB6}"/>
   </bookViews>
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="315" uniqueCount="110">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="316" uniqueCount="110">
   <si>
     <t xml:space="preserve">36.           </t>
   </si>
@@ -486,7 +486,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="5">
+  <borders count="9">
     <border>
       <left/>
       <right/>
@@ -504,15 +504,6 @@
       <top style="thin">
         <color rgb="FF000000"/>
       </top>
-      <bottom style="thin">
-        <color rgb="FF000000"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
       <bottom style="thin">
         <color rgb="FF000000"/>
       </bottom>
@@ -542,11 +533,74 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF000000"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF000000"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF000000"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF000000"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF000000"/>
+      </right>
+      <top/>
+      <bottom style="thin">
+        <color rgb="FF000000"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF000000"/>
+      </left>
+      <right/>
+      <top style="thin">
+        <color rgb="FF000000"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF000000"/>
+      </left>
+      <right/>
+      <top/>
+      <bottom style="thin">
+        <color rgb="FF000000"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="31">
+  <cellXfs count="44">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -575,68 +629,107 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="167" fontId="3" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="3" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="168" fontId="3" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="166" fontId="6" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="168" fontId="3" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="164" fontId="3" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="168" fontId="3" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="166" fontId="6" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="168" fontId="3" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1" shrinkToFit="1"/>
-    </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="164" fontId="3" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="168" fontId="7" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="166" fontId="8" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="top" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="166" fontId="5" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="164" fontId="3" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="168" fontId="7" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="166" fontId="8" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="167" fontId="3" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" shrinkToFit="1"/>
-    </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="166" fontId="5" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="167" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="3" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="168" fontId="7" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="167" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="3" fillId="0" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="166" fontId="8" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="168" fontId="7" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="166" fontId="8" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -1026,13 +1119,13 @@
       </c>
     </row>
     <row r="6" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A6" s="5">
-        <v>13151</v>
+      <c r="A6" s="5" t="s">
+        <v>109</v>
       </c>
       <c r="B6" s="6" t="s">
         <v>8</v>
       </c>
-      <c r="C6" s="30" t="s">
+      <c r="C6" s="24" t="s">
         <v>109</v>
       </c>
       <c r="D6" s="7" t="s">
@@ -1558,10 +1651,10 @@
       </c>
     </row>
     <row r="44" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A44" s="3" t="s">
+      <c r="A44" s="25" t="s">
         <v>83</v>
       </c>
-      <c r="B44" s="6" t="s">
+      <c r="B44" s="26" t="s">
         <v>84</v>
       </c>
       <c r="C44" s="3" t="s">
@@ -1572,59 +1665,59 @@
       </c>
     </row>
     <row r="45" spans="1:6" ht="21.6" x14ac:dyDescent="0.3">
-      <c r="A45" s="10">
+      <c r="A45" s="27">
         <v>36.200000000000003</v>
       </c>
-      <c r="B45" s="11" t="s">
+      <c r="B45" s="28" t="s">
         <v>86</v>
       </c>
-      <c r="C45" s="11"/>
-      <c r="D45" s="11"/>
-      <c r="E45" s="11"/>
-      <c r="F45" s="11"/>
-    </row>
-    <row r="46" spans="1:6" ht="43.2" x14ac:dyDescent="0.3">
-      <c r="A46" s="3" t="s">
+      <c r="C45" s="28"/>
+      <c r="D45" s="28"/>
+      <c r="E45" s="28"/>
+      <c r="F45" s="28"/>
+    </row>
+    <row r="46" spans="1:6" ht="21.6" x14ac:dyDescent="0.3">
+      <c r="A46" s="30" t="s">
         <v>2</v>
       </c>
-      <c r="B46" s="3" t="s">
+      <c r="B46" s="30" t="s">
         <v>3</v>
       </c>
-      <c r="C46" s="3" t="s">
+      <c r="C46" s="30" t="s">
         <v>4</v>
       </c>
-      <c r="D46" s="12" t="s">
+      <c r="D46" s="31" t="s">
         <v>87</v>
       </c>
-      <c r="E46" s="13" t="s">
+      <c r="E46" s="32" t="s">
         <v>88</v>
       </c>
-      <c r="F46" s="12" t="s">
+      <c r="F46" s="31" t="s">
         <v>89</v>
       </c>
     </row>
     <row r="47" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A47" s="14">
+      <c r="A47" s="29">
         <v>-1</v>
       </c>
-      <c r="B47" s="14">
+      <c r="B47" s="29">
         <v>-2</v>
       </c>
-      <c r="C47" s="14">
+      <c r="C47" s="29">
         <v>-3</v>
       </c>
-      <c r="D47" s="14">
+      <c r="D47" s="29">
         <v>-4</v>
       </c>
-      <c r="E47" s="14">
+      <c r="E47" s="29">
         <v>-5</v>
       </c>
-      <c r="F47" s="14">
+      <c r="F47" s="29">
         <v>-6</v>
       </c>
     </row>
     <row r="48" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A48" s="15">
+      <c r="A48" s="11">
         <v>1</v>
       </c>
       <c r="B48" s="6" t="s">
@@ -1633,18 +1726,18 @@
       <c r="C48" s="3" t="s">
         <v>7</v>
       </c>
-      <c r="D48" s="16">
+      <c r="D48" s="12">
         <v>309291000</v>
       </c>
-      <c r="E48" s="16">
+      <c r="E48" s="12">
         <v>401541000</v>
       </c>
-      <c r="F48" s="16">
+      <c r="F48" s="12">
         <v>518306000</v>
       </c>
     </row>
     <row r="49" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A49" s="15">
+      <c r="A49" s="11">
         <v>2</v>
       </c>
       <c r="B49" s="6" t="s">
@@ -1653,18 +1746,18 @@
       <c r="C49" s="3" t="s">
         <v>7</v>
       </c>
-      <c r="D49" s="16">
+      <c r="D49" s="12">
         <v>282447000</v>
       </c>
-      <c r="E49" s="16">
+      <c r="E49" s="12">
         <v>402522000</v>
       </c>
-      <c r="F49" s="16">
+      <c r="F49" s="12">
         <v>501507000</v>
       </c>
     </row>
     <row r="50" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A50" s="15">
+      <c r="A50" s="11">
         <v>3</v>
       </c>
       <c r="B50" s="6" t="s">
@@ -1673,18 +1766,18 @@
       <c r="C50" s="3" t="s">
         <v>7</v>
       </c>
-      <c r="D50" s="16">
+      <c r="D50" s="12">
         <v>317452000</v>
       </c>
-      <c r="E50" s="16">
+      <c r="E50" s="12">
         <v>431233000</v>
       </c>
-      <c r="F50" s="16">
+      <c r="F50" s="12">
         <v>475248000</v>
       </c>
     </row>
     <row r="51" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A51" s="15">
+      <c r="A51" s="11">
         <v>4</v>
       </c>
       <c r="B51" s="6" t="s">
@@ -1693,18 +1786,18 @@
       <c r="C51" s="3" t="s">
         <v>7</v>
       </c>
-      <c r="D51" s="16">
+      <c r="D51" s="12">
         <v>315382000</v>
       </c>
-      <c r="E51" s="16">
+      <c r="E51" s="12">
         <v>375725000</v>
       </c>
-      <c r="F51" s="16">
+      <c r="F51" s="12">
         <v>557486000</v>
       </c>
     </row>
     <row r="52" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A52" s="15">
+      <c r="A52" s="11">
         <v>5</v>
       </c>
       <c r="B52" s="6" t="s">
@@ -1713,18 +1806,18 @@
       <c r="C52" s="3" t="s">
         <v>7</v>
       </c>
-      <c r="D52" s="16">
+      <c r="D52" s="12">
         <v>320418000</v>
       </c>
-      <c r="E52" s="16">
+      <c r="E52" s="12">
         <v>423851000</v>
       </c>
-      <c r="F52" s="16">
+      <c r="F52" s="12">
         <v>565534000</v>
       </c>
     </row>
     <row r="53" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A53" s="15">
+      <c r="A53" s="11">
         <v>6</v>
       </c>
       <c r="B53" s="6" t="s">
@@ -1733,18 +1826,18 @@
       <c r="C53" s="3" t="s">
         <v>7</v>
       </c>
-      <c r="D53" s="16">
+      <c r="D53" s="12">
         <v>284412000</v>
       </c>
-      <c r="E53" s="16">
+      <c r="E53" s="12">
         <v>401040000</v>
       </c>
-      <c r="F53" s="16">
+      <c r="F53" s="12">
         <v>492538000</v>
       </c>
     </row>
     <row r="54" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A54" s="15">
+      <c r="A54" s="11">
         <v>7</v>
       </c>
       <c r="B54" s="6" t="s">
@@ -1753,18 +1846,18 @@
       <c r="C54" s="3" t="s">
         <v>7</v>
       </c>
-      <c r="D54" s="16">
+      <c r="D54" s="12">
         <v>289734000</v>
       </c>
-      <c r="E54" s="16">
+      <c r="E54" s="12">
         <v>430892000</v>
       </c>
-      <c r="F54" s="16">
+      <c r="F54" s="12">
         <v>516336000</v>
       </c>
     </row>
     <row r="55" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A55" s="15">
+      <c r="A55" s="11">
         <v>8</v>
       </c>
       <c r="B55" s="6" t="s">
@@ -1773,18 +1866,18 @@
       <c r="C55" s="3" t="s">
         <v>7</v>
       </c>
-      <c r="D55" s="16">
+      <c r="D55" s="12">
         <v>319121000</v>
       </c>
-      <c r="E55" s="16">
+      <c r="E55" s="12">
         <v>404288000</v>
       </c>
-      <c r="F55" s="16">
+      <c r="F55" s="12">
         <v>491935000</v>
       </c>
     </row>
     <row r="56" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A56" s="15">
+      <c r="A56" s="11">
         <v>9</v>
       </c>
       <c r="B56" s="6" t="s">
@@ -1793,18 +1886,18 @@
       <c r="C56" s="3" t="s">
         <v>7</v>
       </c>
-      <c r="D56" s="16">
+      <c r="D56" s="12">
         <v>338610000</v>
       </c>
-      <c r="E56" s="16">
+      <c r="E56" s="12">
         <v>418511000</v>
       </c>
-      <c r="F56" s="16">
+      <c r="F56" s="12">
         <v>601777000</v>
       </c>
     </row>
     <row r="57" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A57" s="15">
+      <c r="A57" s="11">
         <v>10</v>
       </c>
       <c r="B57" s="6" t="s">
@@ -1813,18 +1906,18 @@
       <c r="C57" s="3" t="s">
         <v>7</v>
       </c>
-      <c r="D57" s="16">
+      <c r="D57" s="12">
         <v>314735000</v>
       </c>
-      <c r="E57" s="16">
+      <c r="E57" s="12">
         <v>431977000</v>
       </c>
-      <c r="F57" s="16">
+      <c r="F57" s="12">
         <v>544094000</v>
       </c>
     </row>
     <row r="58" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A58" s="15">
+      <c r="A58" s="11">
         <v>11</v>
       </c>
       <c r="B58" s="6" t="s">
@@ -1833,18 +1926,18 @@
       <c r="C58" s="3" t="s">
         <v>7</v>
       </c>
-      <c r="D58" s="16">
+      <c r="D58" s="12">
         <v>272285000</v>
       </c>
-      <c r="E58" s="16">
+      <c r="E58" s="12">
         <v>395809000</v>
       </c>
-      <c r="F58" s="16">
+      <c r="F58" s="12">
         <v>504438000</v>
       </c>
     </row>
     <row r="59" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A59" s="15">
+      <c r="A59" s="11">
         <v>12</v>
       </c>
       <c r="B59" s="6" t="s">
@@ -1853,18 +1946,18 @@
       <c r="C59" s="3" t="s">
         <v>7</v>
       </c>
-      <c r="D59" s="16">
+      <c r="D59" s="12">
         <v>300878000</v>
       </c>
-      <c r="E59" s="16">
+      <c r="E59" s="12">
         <v>397179000</v>
       </c>
-      <c r="F59" s="16">
+      <c r="F59" s="12">
         <v>533909000</v>
       </c>
     </row>
     <row r="60" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A60" s="15">
+      <c r="A60" s="11">
         <v>13</v>
       </c>
       <c r="B60" s="6" t="s">
@@ -1873,18 +1966,18 @@
       <c r="C60" s="3" t="s">
         <v>7</v>
       </c>
-      <c r="D60" s="16">
+      <c r="D60" s="12">
         <v>292054000</v>
       </c>
-      <c r="E60" s="16">
+      <c r="E60" s="12">
         <v>434570000</v>
       </c>
-      <c r="F60" s="16">
+      <c r="F60" s="12">
         <v>507692000</v>
       </c>
     </row>
     <row r="61" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A61" s="15">
+      <c r="A61" s="11">
         <v>14</v>
       </c>
       <c r="B61" s="6" t="s">
@@ -1893,18 +1986,18 @@
       <c r="C61" s="3" t="s">
         <v>7</v>
       </c>
-      <c r="D61" s="16">
+      <c r="D61" s="12">
         <v>299447000</v>
       </c>
-      <c r="E61" s="16">
+      <c r="E61" s="12">
         <v>406066000</v>
       </c>
-      <c r="F61" s="16">
+      <c r="F61" s="12">
         <v>532934000</v>
       </c>
     </row>
     <row r="62" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A62" s="15">
+      <c r="A62" s="11">
         <v>15</v>
       </c>
       <c r="B62" s="6" t="s">
@@ -1913,18 +2006,18 @@
       <c r="C62" s="3" t="s">
         <v>7</v>
       </c>
-      <c r="D62" s="16">
+      <c r="D62" s="12">
         <v>311806000</v>
       </c>
-      <c r="E62" s="16">
+      <c r="E62" s="12">
         <v>422257000</v>
       </c>
-      <c r="F62" s="16">
+      <c r="F62" s="12">
         <v>592257000</v>
       </c>
     </row>
     <row r="63" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A63" s="15">
+      <c r="A63" s="11">
         <v>16</v>
       </c>
       <c r="B63" s="6" t="s">
@@ -1933,18 +2026,18 @@
       <c r="C63" s="3" t="s">
         <v>7</v>
       </c>
-      <c r="D63" s="16">
+      <c r="D63" s="12">
         <v>284957000</v>
       </c>
-      <c r="E63" s="16">
+      <c r="E63" s="12">
         <v>406473000</v>
       </c>
-      <c r="F63" s="16">
+      <c r="F63" s="12">
         <v>529092000</v>
       </c>
     </row>
     <row r="64" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A64" s="15">
+      <c r="A64" s="11">
         <v>17</v>
       </c>
       <c r="B64" s="6" t="s">
@@ -1953,18 +2046,18 @@
       <c r="C64" s="3" t="s">
         <v>7</v>
       </c>
-      <c r="D64" s="16">
+      <c r="D64" s="12">
         <v>290070000</v>
       </c>
-      <c r="E64" s="16">
+      <c r="E64" s="12">
         <v>418759000</v>
       </c>
-      <c r="F64" s="16">
+      <c r="F64" s="12">
         <v>543714000</v>
       </c>
     </row>
     <row r="65" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A65" s="15">
+      <c r="A65" s="11">
         <v>18</v>
       </c>
       <c r="B65" s="6" t="s">
@@ -1973,18 +2066,18 @@
       <c r="C65" s="3" t="s">
         <v>7</v>
       </c>
-      <c r="D65" s="16">
+      <c r="D65" s="12">
         <v>321153000</v>
       </c>
-      <c r="E65" s="16">
+      <c r="E65" s="12">
         <v>403789000</v>
       </c>
-      <c r="F65" s="16">
+      <c r="F65" s="12">
         <v>548905000</v>
       </c>
     </row>
     <row r="66" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A66" s="15">
+      <c r="A66" s="11">
         <v>19</v>
       </c>
       <c r="B66" s="6" t="s">
@@ -1993,18 +2086,18 @@
       <c r="C66" s="3" t="s">
         <v>7</v>
       </c>
-      <c r="D66" s="16">
+      <c r="D66" s="12">
         <v>341762000</v>
       </c>
-      <c r="E66" s="16">
+      <c r="E66" s="12">
         <v>460155000</v>
       </c>
-      <c r="F66" s="16">
+      <c r="F66" s="12">
         <v>567031000</v>
       </c>
     </row>
     <row r="67" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A67" s="15">
+      <c r="A67" s="11">
         <v>20</v>
       </c>
       <c r="B67" s="6" t="s">
@@ -2013,18 +2106,18 @@
       <c r="C67" s="3" t="s">
         <v>7</v>
       </c>
-      <c r="D67" s="16">
+      <c r="D67" s="12">
         <v>311313000</v>
       </c>
-      <c r="E67" s="16">
+      <c r="E67" s="12">
         <v>443657000</v>
       </c>
-      <c r="F67" s="16">
+      <c r="F67" s="12">
         <v>593776000</v>
       </c>
     </row>
     <row r="68" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A68" s="15">
+      <c r="A68" s="11">
         <v>21</v>
       </c>
       <c r="B68" s="6" t="s">
@@ -2033,18 +2126,18 @@
       <c r="C68" s="3" t="s">
         <v>7</v>
       </c>
-      <c r="D68" s="16">
+      <c r="D68" s="12">
         <v>360864000</v>
       </c>
-      <c r="E68" s="16">
+      <c r="E68" s="12">
         <v>431180000</v>
       </c>
-      <c r="F68" s="16">
+      <c r="F68" s="12">
         <v>516400000</v>
       </c>
     </row>
     <row r="69" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A69" s="15">
+      <c r="A69" s="11">
         <v>22</v>
       </c>
       <c r="B69" s="6" t="s">
@@ -2053,18 +2146,18 @@
       <c r="C69" s="3" t="s">
         <v>7</v>
       </c>
-      <c r="D69" s="16">
+      <c r="D69" s="12">
         <v>280959000</v>
       </c>
-      <c r="E69" s="16">
+      <c r="E69" s="12">
         <v>446355000</v>
       </c>
-      <c r="F69" s="16">
+      <c r="F69" s="12">
         <v>558727000</v>
       </c>
     </row>
     <row r="70" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A70" s="15">
+      <c r="A70" s="11">
         <v>23</v>
       </c>
       <c r="B70" s="6" t="s">
@@ -2073,18 +2166,18 @@
       <c r="C70" s="3" t="s">
         <v>7</v>
       </c>
-      <c r="D70" s="16">
+      <c r="D70" s="12">
         <v>316276000</v>
       </c>
-      <c r="E70" s="16">
+      <c r="E70" s="12">
         <v>406296000</v>
       </c>
-      <c r="F70" s="16">
+      <c r="F70" s="12">
         <v>554863000</v>
       </c>
     </row>
     <row r="71" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A71" s="15">
+      <c r="A71" s="11">
         <v>24</v>
       </c>
       <c r="B71" s="6" t="s">
@@ -2093,18 +2186,18 @@
       <c r="C71" s="3" t="s">
         <v>7</v>
       </c>
-      <c r="D71" s="16">
+      <c r="D71" s="12">
         <v>304722000</v>
       </c>
-      <c r="E71" s="16">
+      <c r="E71" s="12">
         <v>376200000</v>
       </c>
-      <c r="F71" s="16">
+      <c r="F71" s="12">
         <v>577008000</v>
       </c>
     </row>
     <row r="72" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A72" s="15">
+      <c r="A72" s="11">
         <v>25</v>
       </c>
       <c r="B72" s="6" t="s">
@@ -2113,18 +2206,18 @@
       <c r="C72" s="3" t="s">
         <v>7</v>
       </c>
-      <c r="D72" s="16">
+      <c r="D72" s="12">
         <v>276156000</v>
       </c>
-      <c r="E72" s="16">
+      <c r="E72" s="12">
         <v>376452000</v>
       </c>
-      <c r="F72" s="16">
+      <c r="F72" s="12">
         <v>514131000</v>
       </c>
     </row>
     <row r="73" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A73" s="15">
+      <c r="A73" s="11">
         <v>26</v>
       </c>
       <c r="B73" s="6" t="s">
@@ -2133,18 +2226,18 @@
       <c r="C73" s="3" t="s">
         <v>7</v>
       </c>
-      <c r="D73" s="16">
+      <c r="D73" s="12">
         <v>298447000</v>
       </c>
-      <c r="E73" s="16">
+      <c r="E73" s="12">
         <v>426563000</v>
       </c>
-      <c r="F73" s="16">
+      <c r="F73" s="12">
         <v>514927000</v>
       </c>
     </row>
     <row r="74" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A74" s="15">
+      <c r="A74" s="11">
         <v>27</v>
       </c>
       <c r="B74" s="6" t="s">
@@ -2153,18 +2246,18 @@
       <c r="C74" s="3" t="s">
         <v>7</v>
       </c>
-      <c r="D74" s="16">
+      <c r="D74" s="12">
         <v>459123000</v>
       </c>
-      <c r="E74" s="16">
+      <c r="E74" s="12">
         <v>412948000</v>
       </c>
-      <c r="F74" s="16">
+      <c r="F74" s="12">
         <v>518206000</v>
       </c>
     </row>
     <row r="75" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A75" s="15">
+      <c r="A75" s="11">
         <v>28</v>
       </c>
       <c r="B75" s="6" t="s">
@@ -2173,18 +2266,18 @@
       <c r="C75" s="3" t="s">
         <v>7</v>
       </c>
-      <c r="D75" s="16">
+      <c r="D75" s="12">
         <v>306752000</v>
       </c>
-      <c r="E75" s="16">
+      <c r="E75" s="12">
         <v>452556000</v>
       </c>
-      <c r="F75" s="16">
+      <c r="F75" s="12">
         <v>554368000</v>
       </c>
     </row>
     <row r="76" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A76" s="15">
+      <c r="A76" s="11">
         <v>29</v>
       </c>
       <c r="B76" s="6" t="s">
@@ -2193,18 +2286,18 @@
       <c r="C76" s="3" t="s">
         <v>7</v>
       </c>
-      <c r="D76" s="16">
+      <c r="D76" s="12">
         <v>332671000</v>
       </c>
-      <c r="E76" s="16">
+      <c r="E76" s="12">
         <v>445482000</v>
       </c>
-      <c r="F76" s="16">
+      <c r="F76" s="12">
         <v>541106000</v>
       </c>
     </row>
     <row r="77" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A77" s="15">
+      <c r="A77" s="11">
         <v>30</v>
       </c>
       <c r="B77" s="6" t="s">
@@ -2213,18 +2306,18 @@
       <c r="C77" s="3" t="s">
         <v>7</v>
       </c>
-      <c r="D77" s="16">
+      <c r="D77" s="12">
         <v>329182000</v>
       </c>
-      <c r="E77" s="16">
+      <c r="E77" s="12">
         <v>437198000</v>
       </c>
-      <c r="F77" s="16">
+      <c r="F77" s="12">
         <v>530524000</v>
       </c>
     </row>
     <row r="78" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A78" s="15">
+      <c r="A78" s="11">
         <v>31</v>
       </c>
       <c r="B78" s="6" t="s">
@@ -2233,18 +2326,18 @@
       <c r="C78" s="3" t="s">
         <v>7</v>
       </c>
-      <c r="D78" s="16">
+      <c r="D78" s="12">
         <v>323701000</v>
       </c>
-      <c r="E78" s="16">
+      <c r="E78" s="12">
         <v>427518000</v>
       </c>
-      <c r="F78" s="16">
+      <c r="F78" s="12">
         <v>585988000</v>
       </c>
     </row>
     <row r="79" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A79" s="15">
+      <c r="A79" s="11">
         <v>32</v>
       </c>
       <c r="B79" s="6" t="s">
@@ -2253,18 +2346,18 @@
       <c r="C79" s="3" t="s">
         <v>7</v>
       </c>
-      <c r="D79" s="16">
+      <c r="D79" s="12">
         <v>349162000</v>
       </c>
-      <c r="E79" s="16">
+      <c r="E79" s="12">
         <v>432789000</v>
       </c>
-      <c r="F79" s="16">
+      <c r="F79" s="12">
         <v>537663000</v>
       </c>
     </row>
     <row r="80" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A80" s="17">
+      <c r="A80" s="13">
         <v>33</v>
       </c>
       <c r="B80" s="6" t="s">
@@ -2273,18 +2366,18 @@
       <c r="C80" s="3" t="s">
         <v>7</v>
       </c>
-      <c r="D80" s="16">
+      <c r="D80" s="12">
         <v>331411000</v>
       </c>
-      <c r="E80" s="16">
+      <c r="E80" s="12">
         <v>393635000</v>
       </c>
-      <c r="F80" s="16">
+      <c r="F80" s="12">
         <v>564390000</v>
       </c>
     </row>
     <row r="81" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A81" s="15">
+      <c r="A81" s="11">
         <v>34</v>
       </c>
       <c r="B81" s="6" t="s">
@@ -2293,18 +2386,18 @@
       <c r="C81" s="3" t="s">
         <v>7</v>
       </c>
-      <c r="D81" s="16">
+      <c r="D81" s="12">
         <v>320602000</v>
       </c>
-      <c r="E81" s="16">
+      <c r="E81" s="12">
         <v>424712000</v>
       </c>
-      <c r="F81" s="16">
+      <c r="F81" s="12">
         <v>560900000</v>
       </c>
     </row>
     <row r="82" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A82" s="15">
+      <c r="A82" s="11">
         <v>35</v>
       </c>
       <c r="B82" s="6" t="s">
@@ -2313,18 +2406,18 @@
       <c r="C82" s="3" t="s">
         <v>7</v>
       </c>
-      <c r="D82" s="16">
+      <c r="D82" s="12">
         <v>296853000</v>
       </c>
-      <c r="E82" s="16">
+      <c r="E82" s="12">
         <v>424712000</v>
       </c>
-      <c r="F82" s="16">
+      <c r="F82" s="12">
         <v>560900000</v>
       </c>
     </row>
     <row r="83" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A83" s="15">
+      <c r="A83" s="11">
         <v>36</v>
       </c>
       <c r="B83" s="6" t="s">
@@ -2333,18 +2426,18 @@
       <c r="C83" s="3" t="s">
         <v>7</v>
       </c>
-      <c r="D83" s="16">
+      <c r="D83" s="12">
         <v>319897000</v>
       </c>
-      <c r="E83" s="16">
+      <c r="E83" s="12">
         <v>393635000</v>
       </c>
-      <c r="F83" s="16">
+      <c r="F83" s="12">
         <v>564390000</v>
       </c>
     </row>
     <row r="84" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A84" s="15">
+      <c r="A84" s="11">
         <v>37</v>
       </c>
       <c r="B84" s="6" t="s">
@@ -2353,18 +2446,18 @@
       <c r="C84" s="3" t="s">
         <v>7</v>
       </c>
-      <c r="D84" s="16">
+      <c r="D84" s="12">
         <v>319897000</v>
       </c>
-      <c r="E84" s="16">
+      <c r="E84" s="12">
         <v>393635000</v>
       </c>
-      <c r="F84" s="16">
+      <c r="F84" s="12">
         <v>564390000</v>
       </c>
     </row>
     <row r="85" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A85" s="15">
+      <c r="A85" s="11">
         <v>38</v>
       </c>
       <c r="B85" s="6" t="s">
@@ -2373,31 +2466,31 @@
       <c r="C85" s="3" t="s">
         <v>7</v>
       </c>
-      <c r="D85" s="16">
+      <c r="D85" s="12">
         <v>319897000</v>
       </c>
-      <c r="E85" s="16">
+      <c r="E85" s="12">
         <v>393635000</v>
       </c>
-      <c r="F85" s="16">
+      <c r="F85" s="12">
         <v>564390000</v>
       </c>
     </row>
     <row r="86" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A86" s="18">
+      <c r="A86" s="14">
         <v>36.299999999999997</v>
       </c>
-      <c r="B86" s="19" t="s">
+      <c r="B86" s="15" t="s">
         <v>94</v>
       </c>
-      <c r="C86" s="19"/>
-      <c r="D86" s="19"/>
+      <c r="C86" s="15"/>
+      <c r="D86" s="15"/>
     </row>
     <row r="87" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A87" s="3" t="s">
         <v>2</v>
       </c>
-      <c r="B87" s="20" t="s">
+      <c r="B87" s="16" t="s">
         <v>95</v>
       </c>
       <c r="C87" s="3" t="s">
@@ -2408,767 +2501,767 @@
       </c>
     </row>
     <row r="88" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A88" s="14">
+      <c r="A88" s="10">
         <v>-1</v>
       </c>
-      <c r="B88" s="21">
+      <c r="B88" s="17">
         <v>-2</v>
       </c>
-      <c r="C88" s="14">
+      <c r="C88" s="10">
         <v>-3</v>
       </c>
-      <c r="D88" s="14">
+      <c r="D88" s="10">
         <v>-4</v>
       </c>
     </row>
     <row r="89" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A89" s="22">
+      <c r="A89" s="18">
         <v>1</v>
       </c>
-      <c r="B89" s="23" t="s">
+      <c r="B89" s="19" t="s">
         <v>96</v>
       </c>
-      <c r="C89" s="24" t="s">
+      <c r="C89" s="20" t="s">
         <v>97</v>
       </c>
-      <c r="D89" s="25">
+      <c r="D89" s="21">
         <v>498810000</v>
       </c>
     </row>
     <row r="90" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A90" s="22">
+      <c r="A90" s="33">
         <v>2</v>
       </c>
-      <c r="B90" s="23" t="s">
+      <c r="B90" s="34" t="s">
         <v>98</v>
       </c>
-      <c r="C90" s="24" t="s">
+      <c r="C90" s="38" t="s">
         <v>97</v>
       </c>
-      <c r="D90" s="25">
+      <c r="D90" s="39">
         <v>768820000</v>
       </c>
     </row>
     <row r="91" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A91" s="22">
+      <c r="A91" s="40">
         <v>3</v>
       </c>
-      <c r="B91" s="23" t="s">
+      <c r="B91" s="41" t="s">
         <v>99</v>
       </c>
-      <c r="C91" s="24" t="s">
+      <c r="C91" s="42" t="s">
         <v>97</v>
       </c>
-      <c r="D91" s="25">
+      <c r="D91" s="43">
         <v>1268200000</v>
       </c>
     </row>
     <row r="92" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A92" s="26">
+      <c r="A92" s="35">
         <v>36.4</v>
       </c>
-      <c r="B92" s="27" t="s">
+      <c r="B92" s="36" t="s">
         <v>100</v>
       </c>
-      <c r="C92" s="11"/>
-      <c r="D92" s="11"/>
-      <c r="E92" s="11"/>
+      <c r="C92" s="28"/>
+      <c r="D92" s="28"/>
+      <c r="E92" s="28"/>
     </row>
     <row r="93" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A93" s="3" t="s">
+      <c r="A93" s="30" t="s">
         <v>2</v>
       </c>
-      <c r="B93" s="20" t="s">
+      <c r="B93" s="30" t="s">
         <v>3</v>
       </c>
-      <c r="C93" s="3" t="s">
+      <c r="C93" s="30" t="s">
         <v>4</v>
       </c>
-      <c r="D93" s="3" t="s">
+      <c r="D93" s="30" t="s">
         <v>101</v>
       </c>
-      <c r="E93" s="3" t="s">
+      <c r="E93" s="30" t="s">
         <v>102</v>
       </c>
     </row>
     <row r="94" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A94" s="14">
+      <c r="A94" s="29">
         <v>-1</v>
       </c>
-      <c r="B94" s="21">
+      <c r="B94" s="37">
         <v>-2</v>
       </c>
-      <c r="C94" s="14">
+      <c r="C94" s="29">
         <v>-3</v>
       </c>
-      <c r="D94" s="14">
+      <c r="D94" s="29">
         <v>-4</v>
       </c>
-      <c r="E94" s="14">
+      <c r="E94" s="29">
         <v>-5</v>
       </c>
     </row>
     <row r="95" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A95" s="15">
+      <c r="A95" s="11">
         <v>1</v>
       </c>
-      <c r="B95" s="28" t="s">
+      <c r="B95" s="22" t="s">
         <v>10</v>
       </c>
       <c r="C95" s="3" t="s">
         <v>7</v>
       </c>
-      <c r="D95" s="16">
+      <c r="D95" s="12">
         <v>37464000</v>
       </c>
-      <c r="E95" s="16">
+      <c r="E95" s="12">
         <v>37798000</v>
       </c>
     </row>
     <row r="96" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A96" s="15">
+      <c r="A96" s="11">
         <v>2</v>
       </c>
-      <c r="B96" s="28" t="s">
+      <c r="B96" s="22" t="s">
         <v>12</v>
       </c>
       <c r="C96" s="3" t="s">
         <v>7</v>
       </c>
-      <c r="D96" s="16">
+      <c r="D96" s="12">
         <v>38879000</v>
       </c>
-      <c r="E96" s="16">
+      <c r="E96" s="12">
         <v>41140000</v>
       </c>
     </row>
     <row r="97" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A97" s="15">
+      <c r="A97" s="11">
         <v>3</v>
       </c>
-      <c r="B97" s="28" t="s">
+      <c r="B97" s="22" t="s">
         <v>14</v>
       </c>
       <c r="C97" s="3" t="s">
         <v>7</v>
       </c>
-      <c r="D97" s="16">
+      <c r="D97" s="12">
         <v>35688000</v>
       </c>
-      <c r="E97" s="16">
+      <c r="E97" s="12">
         <v>40258000</v>
       </c>
     </row>
     <row r="98" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A98" s="15">
+      <c r="A98" s="11">
         <v>4</v>
       </c>
-      <c r="B98" s="28" t="s">
+      <c r="B98" s="22" t="s">
         <v>16</v>
       </c>
       <c r="C98" s="3" t="s">
         <v>7</v>
       </c>
-      <c r="D98" s="16">
+      <c r="D98" s="12">
         <v>36727000</v>
       </c>
-      <c r="E98" s="16">
+      <c r="E98" s="12">
         <v>41861000</v>
       </c>
     </row>
     <row r="99" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A99" s="15">
+      <c r="A99" s="11">
         <v>5</v>
       </c>
-      <c r="B99" s="28" t="s">
+      <c r="B99" s="22" t="s">
         <v>18</v>
       </c>
       <c r="C99" s="3" t="s">
         <v>7</v>
       </c>
-      <c r="D99" s="16">
+      <c r="D99" s="12">
         <v>37372000</v>
       </c>
-      <c r="E99" s="16">
+      <c r="E99" s="12">
         <v>39884000</v>
       </c>
     </row>
     <row r="100" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A100" s="15">
+      <c r="A100" s="11">
         <v>6</v>
       </c>
-      <c r="B100" s="28" t="s">
+      <c r="B100" s="22" t="s">
         <v>20</v>
       </c>
       <c r="C100" s="3" t="s">
         <v>7</v>
       </c>
-      <c r="D100" s="16">
+      <c r="D100" s="12">
         <v>36759000</v>
       </c>
-      <c r="E100" s="16">
+      <c r="E100" s="12">
         <v>38087000</v>
       </c>
     </row>
     <row r="101" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A101" s="15">
-        <v>7</v>
-      </c>
-      <c r="B101" s="28" t="s">
+      <c r="A101" s="11">
+        <v>7</v>
+      </c>
+      <c r="B101" s="22" t="s">
         <v>22</v>
       </c>
       <c r="C101" s="3" t="s">
         <v>7</v>
       </c>
-      <c r="D101" s="16">
+      <c r="D101" s="12">
         <v>35009000</v>
       </c>
-      <c r="E101" s="16">
+      <c r="E101" s="12">
         <v>40222000</v>
       </c>
     </row>
     <row r="102" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A102" s="15">
+      <c r="A102" s="11">
         <v>8</v>
       </c>
-      <c r="B102" s="28" t="s">
+      <c r="B102" s="22" t="s">
         <v>24</v>
       </c>
       <c r="C102" s="3" t="s">
         <v>7</v>
       </c>
-      <c r="D102" s="16">
+      <c r="D102" s="12">
         <v>39788000</v>
       </c>
-      <c r="E102" s="16">
+      <c r="E102" s="12">
         <v>36330000</v>
       </c>
     </row>
     <row r="103" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A103" s="15">
+      <c r="A103" s="11">
         <v>9</v>
       </c>
-      <c r="B103" s="28" t="s">
+      <c r="B103" s="22" t="s">
         <v>26</v>
       </c>
       <c r="C103" s="3" t="s">
         <v>7</v>
       </c>
-      <c r="D103" s="16">
+      <c r="D103" s="12">
         <v>41253000</v>
       </c>
-      <c r="E103" s="16">
+      <c r="E103" s="12">
         <v>49325000</v>
       </c>
     </row>
     <row r="104" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A104" s="15">
+      <c r="A104" s="11">
         <v>10</v>
       </c>
-      <c r="B104" s="28" t="s">
+      <c r="B104" s="22" t="s">
         <v>28</v>
       </c>
       <c r="C104" s="3" t="s">
         <v>7</v>
       </c>
-      <c r="D104" s="16">
+      <c r="D104" s="12">
         <v>39873000</v>
       </c>
-      <c r="E104" s="16">
+      <c r="E104" s="12">
         <v>48246000</v>
       </c>
     </row>
     <row r="105" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A105" s="15">
+      <c r="A105" s="11">
         <v>11</v>
       </c>
-      <c r="B105" s="28" t="s">
+      <c r="B105" s="22" t="s">
         <v>30</v>
       </c>
       <c r="C105" s="3" t="s">
         <v>7</v>
       </c>
-      <c r="D105" s="16">
+      <c r="D105" s="12">
         <v>42237000</v>
       </c>
-      <c r="E105" s="16">
+      <c r="E105" s="12">
         <v>37106000</v>
       </c>
     </row>
     <row r="106" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A106" s="15">
+      <c r="A106" s="11">
         <v>12</v>
       </c>
-      <c r="B106" s="28" t="s">
+      <c r="B106" s="22" t="s">
         <v>32</v>
       </c>
       <c r="C106" s="3" t="s">
         <v>7</v>
       </c>
-      <c r="D106" s="16">
+      <c r="D106" s="12">
         <v>36538000</v>
       </c>
-      <c r="E106" s="16">
+      <c r="E106" s="12">
         <v>41917000</v>
       </c>
     </row>
     <row r="107" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A107" s="15">
+      <c r="A107" s="11">
         <v>13</v>
       </c>
-      <c r="B107" s="28" t="s">
+      <c r="B107" s="22" t="s">
         <v>34</v>
       </c>
       <c r="C107" s="3" t="s">
         <v>7</v>
       </c>
-      <c r="D107" s="16">
+      <c r="D107" s="12">
         <v>44384000</v>
       </c>
-      <c r="E107" s="16">
+      <c r="E107" s="12">
         <v>48875000</v>
       </c>
     </row>
     <row r="108" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A108" s="15">
+      <c r="A108" s="11">
         <v>14</v>
       </c>
-      <c r="B108" s="28" t="s">
+      <c r="B108" s="22" t="s">
         <v>90</v>
       </c>
       <c r="C108" s="3" t="s">
         <v>7</v>
       </c>
-      <c r="D108" s="16">
+      <c r="D108" s="12">
         <v>39514000</v>
       </c>
-      <c r="E108" s="16">
+      <c r="E108" s="12">
         <v>42269000</v>
       </c>
     </row>
     <row r="109" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A109" s="15">
+      <c r="A109" s="11">
         <v>15</v>
       </c>
-      <c r="B109" s="28" t="s">
+      <c r="B109" s="22" t="s">
         <v>38</v>
       </c>
       <c r="C109" s="3" t="s">
         <v>7</v>
       </c>
-      <c r="D109" s="16">
+      <c r="D109" s="12">
         <v>39951000</v>
       </c>
-      <c r="E109" s="16">
+      <c r="E109" s="12">
         <v>44102000</v>
       </c>
     </row>
     <row r="110" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A110" s="15">
+      <c r="A110" s="11">
         <v>16</v>
       </c>
-      <c r="B110" s="28" t="s">
+      <c r="B110" s="22" t="s">
         <v>40</v>
       </c>
       <c r="C110" s="3" t="s">
         <v>7</v>
       </c>
-      <c r="D110" s="16">
+      <c r="D110" s="12">
         <v>38461000</v>
       </c>
-      <c r="E110" s="16">
+      <c r="E110" s="12">
         <v>43340000</v>
       </c>
     </row>
     <row r="111" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A111" s="15">
+      <c r="A111" s="11">
         <v>17</v>
       </c>
-      <c r="B111" s="28" t="s">
+      <c r="B111" s="22" t="s">
         <v>42</v>
       </c>
       <c r="C111" s="3" t="s">
         <v>7</v>
       </c>
-      <c r="D111" s="16">
+      <c r="D111" s="12">
         <v>36391000</v>
       </c>
-      <c r="E111" s="16">
+      <c r="E111" s="12">
         <v>43401000</v>
       </c>
     </row>
     <row r="112" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A112" s="15">
+      <c r="A112" s="11">
         <v>18</v>
       </c>
-      <c r="B112" s="28" t="s">
+      <c r="B112" s="22" t="s">
         <v>44</v>
       </c>
       <c r="C112" s="3" t="s">
         <v>7</v>
       </c>
-      <c r="D112" s="16">
+      <c r="D112" s="12">
         <v>39349000</v>
       </c>
-      <c r="E112" s="16">
+      <c r="E112" s="12">
         <v>40946000</v>
       </c>
     </row>
     <row r="113" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A113" s="15">
+      <c r="A113" s="11">
         <v>19</v>
       </c>
-      <c r="B113" s="28" t="s">
+      <c r="B113" s="22" t="s">
         <v>46</v>
       </c>
       <c r="C113" s="3" t="s">
         <v>7</v>
       </c>
-      <c r="D113" s="16">
+      <c r="D113" s="12">
         <v>39253000</v>
       </c>
-      <c r="E113" s="16">
+      <c r="E113" s="12">
         <v>39397000</v>
       </c>
     </row>
     <row r="114" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A114" s="15">
+      <c r="A114" s="11">
         <v>20</v>
       </c>
-      <c r="B114" s="28" t="s">
+      <c r="B114" s="22" t="s">
         <v>48</v>
       </c>
       <c r="C114" s="3" t="s">
         <v>7</v>
       </c>
-      <c r="D114" s="16">
+      <c r="D114" s="12">
         <v>38985000</v>
       </c>
-      <c r="E114" s="16">
+      <c r="E114" s="12">
         <v>41649000</v>
       </c>
     </row>
     <row r="115" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A115" s="15">
+      <c r="A115" s="11">
         <v>21</v>
       </c>
-      <c r="B115" s="28" t="s">
+      <c r="B115" s="22" t="s">
         <v>91</v>
       </c>
       <c r="C115" s="3" t="s">
         <v>7</v>
       </c>
-      <c r="D115" s="16">
+      <c r="D115" s="12">
         <v>37975000</v>
       </c>
-      <c r="E115" s="16">
+      <c r="E115" s="12">
         <v>40583000</v>
       </c>
     </row>
     <row r="116" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A116" s="15">
+      <c r="A116" s="11">
         <v>22</v>
       </c>
-      <c r="B116" s="28" t="s">
+      <c r="B116" s="22" t="s">
         <v>52</v>
       </c>
       <c r="C116" s="3" t="s">
         <v>7</v>
       </c>
-      <c r="D116" s="16">
+      <c r="D116" s="12">
         <v>37349000</v>
       </c>
-      <c r="E116" s="16">
+      <c r="E116" s="12">
         <v>42309000</v>
       </c>
     </row>
     <row r="117" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A117" s="15">
+      <c r="A117" s="11">
         <v>23</v>
       </c>
-      <c r="B117" s="28" t="s">
+      <c r="B117" s="22" t="s">
         <v>54</v>
       </c>
       <c r="C117" s="3" t="s">
         <v>7</v>
       </c>
-      <c r="D117" s="16">
+      <c r="D117" s="12">
         <v>39877000</v>
       </c>
-      <c r="E117" s="16">
+      <c r="E117" s="12">
         <v>42885000</v>
       </c>
     </row>
     <row r="118" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A118" s="15">
+      <c r="A118" s="11">
         <v>24</v>
       </c>
-      <c r="B118" s="28" t="s">
+      <c r="B118" s="22" t="s">
         <v>103</v>
       </c>
       <c r="C118" s="3" t="s">
         <v>7</v>
       </c>
-      <c r="D118" s="16">
+      <c r="D118" s="12">
         <v>37116000</v>
       </c>
-      <c r="E118" s="16">
+      <c r="E118" s="12">
         <v>36670000</v>
       </c>
     </row>
     <row r="119" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A119" s="15">
+      <c r="A119" s="11">
         <v>25</v>
       </c>
-      <c r="B119" s="28" t="s">
+      <c r="B119" s="22" t="s">
         <v>92</v>
       </c>
       <c r="C119" s="3" t="s">
         <v>7</v>
       </c>
-      <c r="D119" s="16">
+      <c r="D119" s="12">
         <v>36558000</v>
       </c>
-      <c r="E119" s="16">
+      <c r="E119" s="12">
         <v>36670000</v>
       </c>
     </row>
     <row r="120" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A120" s="15">
+      <c r="A120" s="11">
         <v>26</v>
       </c>
-      <c r="B120" s="28" t="s">
+      <c r="B120" s="22" t="s">
         <v>60</v>
       </c>
       <c r="C120" s="3" t="s">
         <v>7</v>
       </c>
-      <c r="D120" s="16">
+      <c r="D120" s="12">
         <v>41341000</v>
       </c>
-      <c r="E120" s="16">
+      <c r="E120" s="12">
         <v>39514000</v>
       </c>
     </row>
     <row r="121" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A121" s="15">
+      <c r="A121" s="11">
         <v>27</v>
       </c>
-      <c r="B121" s="28" t="s">
+      <c r="B121" s="22" t="s">
         <v>93</v>
       </c>
       <c r="C121" s="3" t="s">
         <v>7</v>
       </c>
-      <c r="D121" s="16">
+      <c r="D121" s="12">
         <v>36600000</v>
       </c>
-      <c r="E121" s="16">
+      <c r="E121" s="12">
         <v>35503000</v>
       </c>
     </row>
     <row r="122" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A122" s="15">
+      <c r="A122" s="11">
         <v>28</v>
       </c>
-      <c r="B122" s="28" t="s">
+      <c r="B122" s="22" t="s">
         <v>64</v>
       </c>
       <c r="C122" s="3" t="s">
         <v>7</v>
       </c>
-      <c r="D122" s="16">
+      <c r="D122" s="12">
         <v>39997000</v>
       </c>
-      <c r="E122" s="16">
+      <c r="E122" s="12">
         <v>39121000</v>
       </c>
     </row>
     <row r="123" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A123" s="15">
+      <c r="A123" s="11">
         <v>29</v>
       </c>
-      <c r="B123" s="28" t="s">
+      <c r="B123" s="22" t="s">
         <v>66</v>
       </c>
       <c r="C123" s="3" t="s">
         <v>7</v>
       </c>
-      <c r="D123" s="16">
+      <c r="D123" s="12">
         <v>39205000</v>
       </c>
-      <c r="E123" s="16">
+      <c r="E123" s="12">
         <v>44358000</v>
       </c>
     </row>
     <row r="124" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A124" s="15">
+      <c r="A124" s="11">
         <v>30</v>
       </c>
-      <c r="B124" s="28" t="s">
+      <c r="B124" s="22" t="s">
         <v>68</v>
       </c>
       <c r="C124" s="3" t="s">
         <v>7</v>
       </c>
-      <c r="D124" s="16">
+      <c r="D124" s="12">
         <v>38775000</v>
       </c>
-      <c r="E124" s="16">
+      <c r="E124" s="12">
         <v>38184000</v>
       </c>
     </row>
     <row r="125" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A125" s="15">
+      <c r="A125" s="11">
         <v>31</v>
       </c>
-      <c r="B125" s="28" t="s">
+      <c r="B125" s="22" t="s">
         <v>70</v>
       </c>
       <c r="C125" s="3" t="s">
         <v>7</v>
       </c>
-      <c r="D125" s="16">
+      <c r="D125" s="12">
         <v>40950000</v>
       </c>
-      <c r="E125" s="16">
+      <c r="E125" s="12">
         <v>41000000</v>
       </c>
     </row>
     <row r="126" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A126" s="15">
+      <c r="A126" s="11">
         <v>32</v>
       </c>
-      <c r="B126" s="28" t="s">
+      <c r="B126" s="22" t="s">
         <v>72</v>
       </c>
       <c r="C126" s="3" t="s">
         <v>7</v>
       </c>
-      <c r="D126" s="16">
+      <c r="D126" s="12">
         <v>41638000</v>
       </c>
-      <c r="E126" s="16">
+      <c r="E126" s="12">
         <v>41000000</v>
       </c>
     </row>
     <row r="127" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A127" s="17">
+      <c r="A127" s="13">
         <v>33</v>
       </c>
-      <c r="B127" s="28" t="s">
+      <c r="B127" s="22" t="s">
         <v>74</v>
       </c>
       <c r="C127" s="3" t="s">
         <v>7</v>
       </c>
-      <c r="D127" s="16">
+      <c r="D127" s="12">
         <v>40336000</v>
       </c>
-      <c r="E127" s="16">
+      <c r="E127" s="12">
         <v>50095000</v>
       </c>
     </row>
     <row r="128" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A128" s="15">
+      <c r="A128" s="11">
         <v>34</v>
       </c>
-      <c r="B128" s="28" t="s">
+      <c r="B128" s="22" t="s">
         <v>76</v>
       </c>
       <c r="C128" s="3" t="s">
         <v>7</v>
       </c>
-      <c r="D128" s="16">
+      <c r="D128" s="12">
         <v>44401000</v>
       </c>
-      <c r="E128" s="16">
+      <c r="E128" s="12">
         <v>48108000</v>
       </c>
     </row>
     <row r="129" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A129" s="15">
+      <c r="A129" s="11">
         <v>35</v>
       </c>
-      <c r="B129" s="28" t="s">
+      <c r="B129" s="22" t="s">
         <v>78</v>
       </c>
       <c r="C129" s="3" t="s">
         <v>7</v>
       </c>
-      <c r="D129" s="16">
+      <c r="D129" s="12">
         <v>44401000</v>
       </c>
-      <c r="E129" s="16">
+      <c r="E129" s="12">
         <v>48108000</v>
       </c>
     </row>
     <row r="130" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A130" s="15">
+      <c r="A130" s="11">
         <v>36</v>
       </c>
-      <c r="B130" s="28" t="s">
+      <c r="B130" s="22" t="s">
         <v>80</v>
       </c>
       <c r="C130" s="3" t="s">
         <v>7</v>
       </c>
-      <c r="D130" s="16">
+      <c r="D130" s="12">
         <v>40336000</v>
       </c>
-      <c r="E130" s="16">
+      <c r="E130" s="12">
         <v>50095000</v>
       </c>
     </row>
     <row r="131" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A131" s="15">
+      <c r="A131" s="11">
         <v>37</v>
       </c>
-      <c r="B131" s="28" t="s">
+      <c r="B131" s="22" t="s">
         <v>82</v>
       </c>
       <c r="C131" s="3" t="s">
         <v>7</v>
       </c>
-      <c r="D131" s="16">
+      <c r="D131" s="12">
         <v>40336000</v>
       </c>
-      <c r="E131" s="16">
+      <c r="E131" s="12">
         <v>50095000</v>
       </c>
     </row>
     <row r="132" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A132" s="15">
+      <c r="A132" s="11">
         <v>38</v>
       </c>
-      <c r="B132" s="28" t="s">
+      <c r="B132" s="22" t="s">
         <v>84</v>
       </c>
       <c r="C132" s="3" t="s">
         <v>7</v>
       </c>
-      <c r="D132" s="16">
+      <c r="D132" s="12">
         <v>40336000</v>
       </c>
-      <c r="E132" s="16">
+      <c r="E132" s="12">
         <v>50095000</v>
       </c>
     </row>
     <row r="133" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A133" s="18">
+      <c r="A133" s="14">
         <v>36.5</v>
       </c>
-      <c r="B133" s="19" t="s">
+      <c r="B133" s="15" t="s">
         <v>104</v>
       </c>
-      <c r="C133" s="19"/>
-      <c r="D133" s="19"/>
+      <c r="C133" s="15"/>
+      <c r="D133" s="15"/>
     </row>
     <row r="134" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A134" s="3" t="s">
         <v>2</v>
       </c>
-      <c r="B134" s="20" t="s">
+      <c r="B134" s="16" t="s">
         <v>95</v>
       </c>
       <c r="C134" s="3" t="s">
@@ -3179,72 +3272,72 @@
       </c>
     </row>
     <row r="135" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A135" s="14">
+      <c r="A135" s="10">
         <v>-1</v>
       </c>
-      <c r="B135" s="21">
+      <c r="B135" s="17">
         <v>-2</v>
       </c>
-      <c r="C135" s="14">
+      <c r="C135" s="10">
         <v>-3</v>
       </c>
-      <c r="D135" s="14">
+      <c r="D135" s="10">
         <v>-4</v>
       </c>
     </row>
     <row r="136" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A136" s="15">
+      <c r="A136" s="11">
         <v>1</v>
       </c>
-      <c r="B136" s="28" t="s">
+      <c r="B136" s="22" t="s">
         <v>105</v>
       </c>
       <c r="C136" s="3" t="s">
         <v>7</v>
       </c>
-      <c r="D136" s="29">
+      <c r="D136" s="23">
         <v>966804000</v>
       </c>
     </row>
     <row r="137" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A137" s="15">
+      <c r="A137" s="11">
         <v>2</v>
       </c>
-      <c r="B137" s="28" t="s">
+      <c r="B137" s="22" t="s">
         <v>106</v>
       </c>
       <c r="C137" s="3" t="s">
         <v>7</v>
       </c>
-      <c r="D137" s="29">
+      <c r="D137" s="23">
         <v>746110000</v>
       </c>
     </row>
     <row r="138" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A138" s="15">
+      <c r="A138" s="11">
         <v>3</v>
       </c>
-      <c r="B138" s="28" t="s">
+      <c r="B138" s="22" t="s">
         <v>107</v>
       </c>
       <c r="C138" s="3" t="s">
         <v>7</v>
       </c>
-      <c r="D138" s="29">
+      <c r="D138" s="23">
         <v>430080000</v>
       </c>
     </row>
     <row r="139" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A139" s="15">
+      <c r="A139" s="11">
         <v>4</v>
       </c>
-      <c r="B139" s="28" t="s">
+      <c r="B139" s="22" t="s">
         <v>108</v>
       </c>
       <c r="C139" s="3" t="s">
         <v>7</v>
       </c>
-      <c r="D139" s="29">
+      <c r="D139" s="23">
         <v>28000000</v>
       </c>
     </row>
